--- a/human_validation/judge/kor/judge_D011_S001_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S001_P001__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,145 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요—저는 [의사명] 선생입니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 거의 항상 긴장 상태에 있는 느낌이 들어서 왔어요. 그냥 책상에 앉아 있을 때나 댄스의 밤을 즐기려고 할 때조차, 제 몸이 뭔가 나쁜 일에 대비하고 있는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이렇게 계속 긴장되고 곤두선 느낌을 얼마나 오래 느껴오셨나요—몇 달째 계속되고 있나요, 아니면 특정한 일이 있고 나서 좀 더 최근에 시작됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 지금 한 아홉 달 정도 됐어요. 콘도 대출이 압류 쪽으로 흘러가기 시작할 때부터였어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 압류와 재정 문제 외에도, 건강이나 인간관계, 업무 성과 같은 다른 것들에 대해서도 과도하게 걱정하시는 편인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 콘도 문제에만 머물러 있지 않아요. 사촌이 저한테 화나 있는 건 아닌지 걱정하기 시작했다가, 그다음엔 직장에서 상담 전화 중에 실수하지는 않을까 걱정하고, 그다음엔 제가 도대체 어떻게 돈을 모으고 삶을 앞으로 나아가게 할 수 있을지 걱정해요. 그런 식으로 이리저리 옮겨 다녀요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이런 걱정과 함께, 근육 긴장이나 쉽게 피로해지는 느낌, 집중력 저하, 짜증, 수면의 어려움 같은 신체적인 증상도 알아채신 게 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 집중하는 게 힘들었어요. 직장에서 스크립트를 작성하거나 영어나 스페인어로 누군가를 도와주다가, 문득 제가 그냥 화면만 멍하니 보고 있다는 걸 깨달아요. 제 머릿속이 잘못될 수 있는 온갖 것들로 가 있어서, 생각의 흐름을 놓쳐버려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 잠드는 데 어려움을 겪거나, 잠을 유지하는 데 어려움을 겪거나, 잠을 자도 개운하지 않고 뒤척이시는 경우가 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 거의 매일 밤, 침대에 누울 때는 완전히 지쳐 있는데, 머릿속을 끌 수가 없어요. 대출 통지서, 업무 티켓, 제가 놓쳤을지도 모르는 것들을 계속 되풀이해서 생각하다 보면 어느새 새벽 두세 시가 돼 있어요. 잠이 들어도 거의 쉬지 못한 것 같은 느낌으로 깨요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 지난 몇 달 동안 사람들에게 더 짜증이 나거나 쉽게 화가 난다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 사람들한테 특별히 더 짜증을 내게 됐다고 느낀 적은 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>진단명: 범불안장애 (D011)
 인구통계: 성별 여성 / 나이 29 / 직업상태 computer support specialist / 최종학력 대학원 졸업
@@ -575,194 +705,36 @@
 증상 지속 기간: 9 months
 추가 요건: 
 주호소 증상 코드: S058
-배경 서술: 아나벨라는 사촌과 함께 소형 콘도 대출에 공동 서명을 했는데, 이를 가족 투자이자 독립을 향한 한 걸음으로 여겼다. 하지만 사촌의 근무 시간이 줄고 예상치 못한 수리비가 겹치면서 대출은 압류 절차로 이어졌다. 처음에는 이를 또 하나의 복잡한 프로젝트처럼 취급해서 컴퓨터 지원 업무 티켓 사이사이에 스프레드시트를 만들고 지역사회 기술 멘토링도 계속했지만, 이후 9개월에 걸쳐 그녀의 걱정은 압류 문제를 넘어 업무 성과, 가족을 실망시킬 것에 대한 걱정, 재정, 미래 계획으로까지 번져갔다. 수면이 불규칙해졌고, 헬프데스크 업무의 긴급 상황에서도 댄스의 밤에서도 긴장을 늦추지 못했으며, 평소에는 정확하게 처리하던 스크립팅 작업과 이중언어 지원 전화에서 집중력을 잃기 시작했다. 지속적인 피로와 불면 때문에 찾아간 1차 진료 의사가 그녀의 전반적이고 통제되지 않는 걱정 패턴을 알아차리고 평가를 의뢰하면서, 그녀는 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요—저는 [의사명] 선생입니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 거의 항상 긴장 상태에 있는 느낌이 들어서 왔어요. 그냥 책상에 앉아 있을 때나 댄스의 밤을 즐기려고 할 때조차, 제 몸이 뭔가 나쁜 일에 대비하고 있는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이렇게 계속 긴장되고 곤두선 느낌을 얼마나 오래 느껴오셨나요—몇 달째 계속되고 있나요, 아니면 특정한 일이 있고 나서 좀 더 최근에 시작됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 지금 한 아홉 달 정도 됐어요. 콘도 대출이 압류 쪽으로 흘러가기 시작할 때부터였어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 압류와 재정 문제 외에도, 건강이나 인간관계, 업무 성과 같은 다른 것들에 대해서도 과도하게 걱정하시는 편인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 콘도 문제에만 머물러 있지 않아요. 사촌이 저한테 화나 있는 건 아닌지 걱정하기 시작했다가, 그다음엔 직장에서 상담 전화 중에 실수하지는 않을까 걱정하고, 그다음엔 제가 도대체 어떻게 돈을 모으고 삶을 앞으로 나아가게 할 수 있을지 걱정해요. 그런 식으로 이리저리 옮겨 다녀요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이런 걱정과 함께, 근육 긴장이나 쉽게 피로해지는 느낌, 집중력 저하, 짜증, 수면의 어려움 같은 신체적인 증상도 알아채신 게 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 집중하는 게 힘들었어요. 직장에서 스크립트를 작성하거나 영어나 스페인어로 누군가를 도와주다가, 문득 제가 그냥 화면만 멍하니 보고 있다는 걸 깨달아요. 제 머릿속이 잘못될 수 있는 온갖 것들로 가 있어서, 생각의 흐름을 놓쳐버려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 잠드는 데 어려움을 겪거나, 잠을 유지하는 데 어려움을 겪거나, 잠을 자도 개운하지 않고 뒤척이시는 경우가 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 거의 매일 밤, 침대에 누울 때는 완전히 지쳐 있는데, 머릿속을 끌 수가 없어요. 대출 통지서, 업무 티켓, 제가 놓쳤을지도 모르는 것들을 계속 되풀이해서 생각하다 보면 어느새 새벽 두세 시가 돼 있어요. 잠이 들어도 거의 쉬지 못한 것 같은 느낌으로 깨요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 지난 몇 달 동안 사람들에게 더 짜증이 나거나 쉽게 화가 난다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 사람들한테 특별히 더 짜증을 내게 됐다고 느낀 적은 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+배경 서술: 아나벨라는 사촌과 함께 소형 콘도 대출에 공동 서명을 했는데, 이를 가족 투자이자 독립을 향한 한 걸음으로 여겼다. 하지만 사촌의 근무 시간이 줄고 예상치 못한 수리비가 겹치면서 대출은 압류 절차로 이어졌다. 처음에는 이를 또 하나의 복잡한 프로젝트처럼 취급해서 컴퓨터 지원 업무 티켓 사이사이에 스프레드시트를 만들고 지역사회 기술 멘토링도 계속했지만, 이후 9개월에 걸쳐 그녀의 걱정은 압류 문제를 넘어 업무 성과, 가족을 실망시킬 것에 대한 걱정, 재정, 미래 계획으로까지 번져갔다. 수면이 불규칙해졌고, 헬프데스크 업무의 긴급 상황에서도 댄스의 밤에서도 긴장을 늦추지 못했으며, 평소에는 정확하게 처리하던 스크립팅 작업과 이중언어 지원 전화에서 집중력을 잃기 시작했다. 지속적인 피로와 불면 때문에 찾아간 1차 진료 의사가 그녀의 전반적이고 통제되지 않는 걱정 패턴을 알아차리고 평가를 의뢰하면서, 그녀는 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S056 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.
+  - S057 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.
+  - S058 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.
+  - S059 집중 곤란: 집중하는 데 어려움을 겪거나 머릿속이 하얘짐.</t>
+        </is>
+      </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 범불안장애 (D011, ICD: F41.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: anxiety_symptoms (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.; 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.; 집중 곤란: 집중하는 데 어려움을 겪거나 머릿속이 하얘짐.
-  누락: 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 통제 불가능한 걱정: 걱정을 멈추거나 조절하기 어렵다는 주관적 경험.; 과민성: 사소한 자극에도 민감하거나 날카롭게 반응하는 상태.; 근육 긴장: 근육이 지속적으로 긴장되고 뻣뻣하며 불편감을 동반하는 상태.</t>
+          <t>의사의 최종 진단: 범불안장애 (D011, ICD: F41.1)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: anxiety_symptoms (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 과도한 불안/걱정: 여러 사건이나 활동에 대해 과도한 불안과 걱정(예기 불안)이 지속적으로 나타남.
+  - 안절부절/긴장감: 안절부절못하거나 곤두선 느낌 또는 신경이 날카로운 느낌.
+  - 집중 곤란: 집중하는 데 어려움을 겪거나 머릿속이 하얘짐.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D011_S001_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S001_P001__claude-sonnet-5_kor.xlsx
@@ -691,6 +691,11 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -730,11 +735,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D011_S001_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D011_S001_P001__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.5303</v>
+        <v>0.5417</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.697</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
